--- a/tools/importer/reports/import-turner-about.report.xlsx
+++ b/tools/importer/reports/import-turner-about.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="99">
   <si>
     <t>_reportFile</t>
   </si>
@@ -151,7 +151,7 @@
     <t>tangent-energy/en-us</t>
   </si>
   <si>
-    <t>2026-08-22T12:54:22.410Z</t>
+    <t>2026-08-24T08:03:38.972Z</t>
   </si>
   <si>
     <t>turner-powertrain/en-us.report.json</t>
@@ -166,7 +166,7 @@
     <t>turner-home</t>
   </si>
   <si>
-    <t>2026-08-22T13:42:42.357Z</t>
+    <t>2026-08-24T08:04:27.919Z</t>
   </si>
   <si>
     <t>Turner | Turner Power Train</t>
@@ -181,7 +181,7 @@
     <t>tangent-energy/en-us/about-us</t>
   </si>
   <si>
-    <t>2026-08-22T12:54:28.865Z</t>
+    <t>2026-08-24T08:03:48.169Z</t>
   </si>
   <si>
     <t>tangent-energy/en-us/customer-segments.report.json</t>
@@ -190,7 +190,7 @@
     <t>tangent-energy/en-us/customer-segments</t>
   </si>
   <si>
-    <t>2026-08-22T12:54:44.951Z</t>
+    <t>2026-08-24T08:04:08.234Z</t>
   </si>
   <si>
     <t>tangent-energy/en-us/meet-the-team.report.json</t>
@@ -199,7 +199,7 @@
     <t>tangent-energy/en-us/meet-the-team</t>
   </si>
   <si>
-    <t>2026-08-22T12:54:36.480Z</t>
+    <t>2026-08-24T08:03:58.674Z</t>
   </si>
   <si>
     <t>tangent-energy/en-us/tangent-amp.report.json</t>
@@ -208,7 +208,7 @@
     <t>tangent-energy/en-us/tangent-amp</t>
   </si>
   <si>
-    <t>2026-08-22T12:54:52.259Z</t>
+    <t>2026-08-24T08:04:17.475Z</t>
   </si>
   <si>
     <t>turner-powertrain/en-us/about-us.report.json</t>
@@ -223,7 +223,7 @@
     <t>turner-about</t>
   </si>
   <si>
-    <t>2026-08-24T05:41:54.017Z</t>
+    <t>2026-08-24T08:05:04.351Z</t>
   </si>
   <si>
     <t>About Us | Turner Power Train</t>
@@ -232,10 +232,31 @@
     <t>https://www.turner-powertrain.com/en_US/about-us.html</t>
   </si>
   <si>
+    <t>turner-powertrain/en-us/knowledge-hub.report.json</t>
+  </si>
+  <si>
+    <t>["page-hero","resource-cards","columns-media"]</t>
+  </si>
+  <si>
+    <t>turner-powertrain/en-us/knowledge-hub</t>
+  </si>
+  <si>
+    <t>turner-knowledge-hub</t>
+  </si>
+  <si>
+    <t>2026-08-24T06:45:48.248Z</t>
+  </si>
+  <si>
+    <t>Knowledge Hub | Turner Power Train</t>
+  </si>
+  <si>
+    <t>https://www.turner-powertrain.com/en_US/knowledge-hub.html</t>
+  </si>
+  <si>
     <t>turner-powertrain/en-us/products.report.json</t>
   </si>
   <si>
-    <t>[]</t>
+    <t>["resource-cards"]</t>
   </si>
   <si>
     <t>turner-powertrain/en-us/products</t>
@@ -244,7 +265,7 @@
     <t>turner-products</t>
   </si>
   <si>
-    <t>2026-08-24T05:41:32.300Z</t>
+    <t>2026-08-24T08:04:37.590Z</t>
   </si>
   <si>
     <t>Products | Turner Power Train</t>
@@ -265,7 +286,7 @@
     <t>turner-product-detail</t>
   </si>
   <si>
-    <t>2026-08-24T05:41:39.126Z</t>
+    <t>2026-08-24T08:04:46.674Z</t>
   </si>
   <si>
     <t>C90 | Turner Power Train</t>
@@ -280,7 +301,7 @@
     <t>turner-powertrain/en-us/products/pg145</t>
   </si>
   <si>
-    <t>2026-08-24T05:41:46.763Z</t>
+    <t>2026-08-24T08:04:53.488Z</t>
   </si>
   <si>
     <t>PG145 | Turner Power Train</t>
@@ -675,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="50" customWidth="1"/>
@@ -1080,25 +1101,51 @@
         <v>87</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G16" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" t="s">
         <v>88</v>
       </c>
-      <c r="D16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" t="s">
-        <v>83</v>
-      </c>
-      <c r="F16" t="s">
-        <v>89</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="C17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
         <v>90</v>
       </c>
-      <c r="H16" t="s">
-        <v>91</v>
+      <c r="F17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G17" t="s">
+        <v>97</v>
+      </c>
+      <c r="H17" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
